--- a/AAII_Financials/Quarterly/ETRN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETRN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
   <si>
     <t>ETRN</t>
   </si>
@@ -656,391 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>360600</v>
+      </c>
+      <c r="E8" s="3">
         <v>338500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>318500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>376300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>355200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>331800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>328600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>342100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>246700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>342100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>348300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>380000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>367100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>350000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>340600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>453100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>425900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>408400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>406200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>389800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>384800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>364600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>374700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>371000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>206300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>396900</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E9" s="3">
         <v>43000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>45800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>42900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>54100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>35300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>32400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>33100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>42200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>38700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>38200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>34100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>40100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>33900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>41700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>38400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>47900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>43000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>46600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>27900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>44700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>48100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>43300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>27200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>19600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>35100</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>314300</v>
+      </c>
+      <c r="E10" s="3">
         <v>295500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>272700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>333400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>301100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>296500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>296200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>309000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>204500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>303400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>310100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>345900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>327000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>316100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>298900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>414700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>378000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>365400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>359600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>361900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>340100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>316500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>331400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>343800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>186700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>361800</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1071,8 +1083,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1157,8 +1170,11 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,8 +1259,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1254,169 +1273,175 @@
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>583100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>24900</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>1926400</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>56200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>41000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>11500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>91800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>585100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>305700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>95700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>8800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>299400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>16700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>15700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>15600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>3900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1500</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>86800</v>
+      </c>
+      <c r="E15" s="3">
         <v>85600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>86200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>85600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>85100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>84800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>83900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>83200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>82700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>82200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>85500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>84800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>84500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>83000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>79400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>75900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>75200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>74000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>70500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>60900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>59000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>54100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>52600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>51700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>22200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>41900</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>175300</v>
+      </c>
+      <c r="E17" s="3">
         <v>184200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>188900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>161100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>177200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>736500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>170300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>146000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2083800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>154500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>215300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>195400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>160400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>149500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>165300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>235900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>737600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>446900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>240000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>129700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>444200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>146300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>139800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>121700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>65000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>113600</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>185300</v>
+      </c>
+      <c r="E18" s="3">
         <v>154300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>129600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>215200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>178000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-404700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>158400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>196100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1837100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>187600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>133000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>184600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>206700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>200500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>175300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>217200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-311700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-38500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>166200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>260100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-59400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>218300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>234900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>249300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>141300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>283300</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,180 +1680,187 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-39800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-35500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-60200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-112900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-112400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-98600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-90900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-81200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>31100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>16800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>9100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>42300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>84300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>70800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>59700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>52500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>46200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>39100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>34500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-18900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-19400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>232300</v>
+      </c>
+      <c r="E21" s="3">
         <v>204300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>155600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>187900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>150700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-418500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>151300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>282300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1835600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>300900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>235300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>278400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>333500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>367800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>325500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>352900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-184000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>81700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>275800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>355500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-19300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>253000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>279400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>298700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>160000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>322900</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1843,48 +1882,48 @@
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
         <v>94500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>95200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>95500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>97100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>96600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>88900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>87900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>68400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>68300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>69400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>67200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>63300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>62500</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1894,8 +1933,8 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -1906,180 +1945,189 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>145500</v>
+      </c>
+      <c r="E23" s="3">
         <v>118700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>69400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>102300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>65600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-503300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>67400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>104500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2013400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>123100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>52700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>97000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>160100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>196900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>177700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>208700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-328700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-59500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>142000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>232000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-78300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>198900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>226900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>247000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>137700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>280900</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-11000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-3800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-408500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>32200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>12600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>20400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>23500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>28400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>34300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>19100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>11500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>32500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>32300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>12900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>23200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>22300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>46100</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E26" s="3">
         <v>129700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>68900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>106100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>67700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-502900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>64700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>98900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1604900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>90900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>40100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>76600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>136600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>168400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>143500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>189600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-333500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-61500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>130500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>199600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-110600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>186000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>219600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>223700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>115500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>234900</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>134200</v>
+      </c>
+      <c r="E27" s="3">
         <v>112800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>52600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>87100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>51600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-520500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>46200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>80500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1623600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>72700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>22500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>58100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>117800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>149800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>27000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>69700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-268700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-65800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>74500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>56300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-40800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>82800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>101100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>82700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>33300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>66600</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2466,17 +2526,17 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>3</v>
+      <c r="S29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>3</v>
@@ -2484,12 +2544,12 @@
       <c r="V29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X29" s="3">
         <v>-7400</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2508,8 +2568,11 @@
       <c r="AD29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,180 +2746,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E32" s="3">
         <v>35500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>60200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>112900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>112400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>98600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>90900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>81200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-31100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-16800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-9100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-42300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-84300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-70800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-59700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-52500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-46200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-39100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-34500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>18900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>19400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>8000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2300</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>134200</v>
+      </c>
+      <c r="E33" s="3">
         <v>112800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>52600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>87100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>51600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-520500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>46200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>80500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1623600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>72700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>22500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>58100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>117800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>149800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>27000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>69700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-268700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-65800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>74500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>56300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-48200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>82800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>101100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>82700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>33300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>66600</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>134200</v>
+      </c>
+      <c r="E35" s="3">
         <v>112800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>52600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>87100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>51600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-520500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>46200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>80500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1623600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>72700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>22500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>58100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>117800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>149800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>27000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>69700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-268700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-65800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>74500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>56300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-48200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>82800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>101100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>82700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>33300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>66600</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,80 +3264,81 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>258900</v>
+      </c>
+      <c r="E41" s="3">
         <v>180600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>107100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>52500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>67900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>48100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>114500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>41600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>134700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>194200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>242600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>231900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>208000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>182500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>202300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>76000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>88300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>153800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>25500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>29000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>294200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>184100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1847400</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3265,8 +3351,11 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3351,80 +3440,83 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>258300</v>
+      </c>
+      <c r="E43" s="3">
         <v>240000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>237600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>225700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>246900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>230900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>227600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>232000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>252300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>238500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>254900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>288700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>290400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>263700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>238500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>253200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>255300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>243500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>282800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>265100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>255500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>225800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>233900</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3437,8 +3529,11 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3523,80 +3618,83 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>78400</v>
+      </c>
+      <c r="E45" s="3">
         <v>67200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>71000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>43000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>74900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>53100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>49600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>52300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>59900</v>
-      </c>
-      <c r="L45" s="3">
-        <v>53000</v>
       </c>
       <c r="M45" s="3">
         <v>53000</v>
       </c>
       <c r="N45" s="3">
+        <v>53000</v>
+      </c>
+      <c r="O45" s="3">
         <v>51600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>63300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>86900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>62400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>39300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>31500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>24900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>25000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>16800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>19200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>10300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>14600</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3609,80 +3707,83 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>595500</v>
+      </c>
+      <c r="E46" s="3">
         <v>487800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>415700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>321200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>389700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>332100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>391700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>325900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>446800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>485800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>550600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>572200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>561700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>533000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>503200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>368400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>375200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>422200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>333300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>311000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>568800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>420300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2095900</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3695,80 +3796,83 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1832300</v>
+      </c>
+      <c r="E47" s="3">
         <v>1291000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1090200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>852000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>819700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>784400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1325700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1279000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1239000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3089100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2971700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2870200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2796300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2722100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2592400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2465800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2324100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2227300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2066300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1673300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1510300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1300400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1003300</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3781,80 +3885,83 @@
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7992400</v>
+      </c>
+      <c r="E48" s="3">
         <v>7949500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7910900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7900700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7884300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7858700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7822400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7783600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7787500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7773200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7762100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7816000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7881100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7838700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7806900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7750800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7787600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7679800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7446700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6055300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5867600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5620200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5401800</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3867,80 +3974,83 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1008800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1025000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1041200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1057400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1073700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1089900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1106100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1122300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1138500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1154700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1170900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1187100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1203300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1219500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1235700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1251900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1284100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1882400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2216100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1805000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1815400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1971400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1981800</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3953,8 +4063,11 @@
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,80 +4241,83 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>280400</v>
+      </c>
+      <c r="E52" s="3">
         <v>279300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>269000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>267700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>278200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>321400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>316100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>308000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>270700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>365600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>351000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>343300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>283400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>317300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>307000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>352800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>270700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>364300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>374100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>430700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>761700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>630500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>580100</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4211,8 +4330,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,80 +4419,83 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11709400</v>
+      </c>
+      <c r="E54" s="3">
         <v>11032700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10727000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10399100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10445600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10386500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10961900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10818700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10882500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12868400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12806300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12788800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12725900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>12630700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>12445300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>12189700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12041700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>12576000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>12436500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10275400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10523800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9942800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>11062900</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4383,8 +4508,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,80 +4576,81 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>60900</v>
+      </c>
+      <c r="E57" s="3">
         <v>54000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>49500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>43900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>60500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>51200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>61300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>47600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>59600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>64200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>61800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>67700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>72100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>101100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>111700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>109200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>128100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>173000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>181100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>142500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>210000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>133600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>115500</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4533,34 +4663,37 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>299700</v>
+      </c>
+      <c r="E58" s="3">
         <v>299600</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>98900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>98800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>98900</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -4569,22 +4702,22 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>310000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>302500</v>
       </c>
       <c r="P58" s="3">
         <v>302500</v>
       </c>
       <c r="Q58" s="3">
-        <v>0</v>
+        <v>302500</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3">
         <v>6000</v>
@@ -4598,8 +4731,8 @@
       <c r="W58" s="3">
         <v>6000</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
+      <c r="X58" s="3">
+        <v>6000</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
@@ -4619,80 +4752,83 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>422300</v>
+      </c>
+      <c r="E59" s="3">
         <v>297300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>412400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>170000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>254000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>391100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>239100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>160100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>307900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>254000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>310700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>197200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>220300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>268700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>290900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>184000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>201800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>379400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>506800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>244800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>333400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>824700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>793000</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4705,80 +4841,83 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>782900</v>
+      </c>
+      <c r="E60" s="3">
         <v>650900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>461900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>312900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>413300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>541200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>300400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>207700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>367600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>318200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>372500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>574800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>594900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>672300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>402600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>293100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>336000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>558300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>693900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>393300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>549500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>958300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>908500</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4791,80 +4930,83 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7276700</v>
+      </c>
+      <c r="E61" s="3">
         <v>6884000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6910900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6830600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6870300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6727400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6848900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6885700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6939900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7077200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7079400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6911700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6928300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6925600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7225500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6582600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6324500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5978100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5394100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5115200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4660200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3477300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3714000</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -4877,79 +5019,82 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1461700</v>
+      </c>
+      <c r="E62" s="3">
         <v>1343300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1254500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1153800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1081500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>994400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1093700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1005200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>920700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1132000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1027700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>940100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>839500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>711200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>600000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>269600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>99200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>98300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>103300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>89800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>54500</v>
-      </c>
-      <c r="X62" s="3">
-        <v>31800</v>
       </c>
       <c r="Y62" s="3">
         <v>31800</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
+      <c r="Z62" s="3">
+        <v>31800</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
@@ -4963,8 +5108,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,80 +5375,83 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9983900</v>
+      </c>
+      <c r="E66" s="3">
         <v>9343600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9092700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8773100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8844500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8740900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8734000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8585500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8711400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9006600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8955200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8899100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8833900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8776200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8691200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11752800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11369000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11430900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11110200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8912200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10066000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9684600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9677600</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5307,8 +5464,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5556,11 +5723,11 @@
         <v>681800</v>
       </c>
       <c r="Q70" s="3">
+        <v>681800</v>
+      </c>
+      <c r="R70" s="3">
         <v>669500</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -5597,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,80 +5853,83 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2932200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3000900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3047300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3031700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3053600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3003800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2417000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2407300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2464600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-770800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-778200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-735900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-729000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-781400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-866100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-858400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-618100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-234300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-53800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-13700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>33900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>258200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1385300</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5769,8 +5942,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,80 +6209,83 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1043700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1007200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>952500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>944200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>919200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>963800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1546100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1551300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1489300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3180000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3169300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3207900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3210100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3172600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3084600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>436900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>672700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1145100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1326200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1363200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>457800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>258200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1385300</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6113,8 +6298,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>134200</v>
+      </c>
+      <c r="E81" s="3">
         <v>112800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>52600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>87100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>51600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-520500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>46200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>80500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1623600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>72700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>22500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>58100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>117800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>149800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>27000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>69700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-268700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-65800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>74500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>56300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-48200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>82800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>101100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>82700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>33300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>66600</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,94 +6605,98 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>86800</v>
+      </c>
+      <c r="E83" s="3">
         <v>85600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>86200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>85600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>85100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>84800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>83900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>83200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>82700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>82200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>85500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>84800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>84500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>83000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>79400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>75900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>75200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>74000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>70500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>60900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>59000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>54100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>52600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>51700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>22200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>41900</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,94 +7137,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>291200</v>
+      </c>
+      <c r="E89" s="3">
         <v>201600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>298600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>224700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>99200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>209600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>351000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>185900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>346700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>209900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>382600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>229600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>316700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>231200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>343700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>249300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>286000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>267900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>300300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>122200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>20300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>251800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>154900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>294700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>160000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>320500</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,94 +7261,98 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-107100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-107500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-96300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-75600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-99800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-113700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-91900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-71300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-79400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-80700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-69100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-61300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-84400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-108500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-116700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-152400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-197400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-287400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-273600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-209000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-241500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-241400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-212400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-170600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-75200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-149400</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,94 +7526,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-514500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-316000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-130900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-108700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-139900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-155000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-129700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-142500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-186800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-173700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-141700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-70700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-211700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-172900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-148900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-196300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-458000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-486500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1277500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-352600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-718800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-503500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-277100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-286500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-117600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-207300</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7433,7 +7666,7 @@
         <v>-65000</v>
       </c>
       <c r="G96" s="3">
-        <v>-64900</v>
+        <v>-65000</v>
       </c>
       <c r="H96" s="3">
         <v>-64900</v>
@@ -7457,20 +7690,20 @@
         <v>-64900</v>
       </c>
       <c r="O96" s="3">
+        <v>-64900</v>
+      </c>
+      <c r="P96" s="3">
         <v>213500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-64900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-34400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-114300</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -7481,11 +7714,11 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>20800</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -7504,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,94 +8004,100 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>301500</v>
+      </c>
+      <c r="E100" s="3">
         <v>187900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-113100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-131400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>60500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-121000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-148400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-136500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-219500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-84600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-230200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-135000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-79500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-78100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-68400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-65300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>106500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>346800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>923600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>15300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>808600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1411500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1803200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>37100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-197500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-718900</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7934,90 +8182,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E102" s="3">
         <v>73500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>54600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-15400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>19800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-66500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>72900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-93100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-59600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-48400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>10700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>23900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>25500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-19800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>126400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-12400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-65400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>128300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-53500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-215100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>110100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1663300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1681100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>45300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-155100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-605700</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ETRN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETRN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
   <si>
     <t>ETRN</t>
   </si>
@@ -656,403 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>364300</v>
+      </c>
+      <c r="E8" s="3">
         <v>360600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>338500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>318500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>376300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>355200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>331800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>328600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>342100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>246700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>342100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>348300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>380000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>367100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>350000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>340600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>453100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>425900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>408400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>406200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>389800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>384800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>364600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>374700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>371000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>206300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>396900</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>45200</v>
+      </c>
+      <c r="E9" s="3">
         <v>46300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>43000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>45800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>42900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>54100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>35300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>32400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>33100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>42200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>38700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>38200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>34100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>40100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>33900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>41700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>38400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>47900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>43000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>46600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>27900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>44700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>48100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>43300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>27200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>19600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>35100</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>319100</v>
+      </c>
+      <c r="E10" s="3">
         <v>314300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>295500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>272700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>333400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>301100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>296500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>296200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>309000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>204500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>303400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>310100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>345900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>327000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>316100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>298900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>414700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>378000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>365400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>359600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>361900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>340100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>316500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>331400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>343800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>186700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>361800</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,13 +1279,16 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1276,172 +1296,178 @@
       <c r="F14" s="3">
         <v>0</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>583100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>24900</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>1926400</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>56200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>41000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>1000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>11500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>91800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>585100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>305700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>95700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>8800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>299400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>16700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>15700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>15600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>3900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1500</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>87900</v>
+      </c>
+      <c r="E15" s="3">
         <v>86800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>85600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>86200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>85600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>85100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>84800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>83900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>83200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>82700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>82200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>85500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>84800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>84500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>83000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>79400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>75900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>75200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>74000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>70500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>60900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>59000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>54100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>52600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>51700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>22200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>41900</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>183100</v>
+      </c>
+      <c r="E17" s="3">
         <v>175300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>184200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>188900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>161100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>177200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>736500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>170300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>146000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2083800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>154500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>215300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>195400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>160400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>149500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>165300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>235900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>737600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>446900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>240000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>129700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>444200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>146300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>139800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>121700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>65000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>113600</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>181200</v>
+      </c>
+      <c r="E18" s="3">
         <v>185300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>154300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>129600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>215200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>178000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-404700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>158400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>196100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1837100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>187600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>133000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>184600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>206700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>200500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>175300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>217200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-311700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-38500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>166200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>260100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-59400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>218300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>234900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>249300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>141300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>283300</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,186 +1714,193 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-49900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-39800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-35500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-60200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-112900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-112400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-98600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-90900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-81200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>31100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>16800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>9100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>42300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>84300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>70800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>59700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>52500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>46200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>39100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>34500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-18900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-19400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>219200</v>
+      </c>
+      <c r="E21" s="3">
         <v>232300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>204300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>155600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>187900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>150700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-418500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>151300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>282300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1835600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>300900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>235300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>278400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>333500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>367800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>325500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>352900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-184000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>81700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>275800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>355500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-19300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>253000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>279400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>298700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>160000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>322900</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1885,48 +1925,48 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
         <v>94500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>95200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>95500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>97100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>96600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>88900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>87900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>68400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>68300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>69400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>67200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>63300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>62500</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1936,8 +1976,8 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -1948,186 +1988,195 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>131300</v>
+      </c>
+      <c r="E23" s="3">
         <v>145500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>118700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>69400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>102300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>65600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-503300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>67400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>104500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2013400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>123100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>52700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>97000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>160100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>196900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>177700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>208700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-328700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-59500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>142000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>232000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-78300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>198900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>226900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>247000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>137700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>280900</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-4500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-11000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-3800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-408500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>32200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>20400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>23500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>28400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>34300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>19100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>11500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>32500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>32300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>12900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>23200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>22300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>46100</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>111900</v>
+      </c>
+      <c r="E26" s="3">
         <v>150000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>129700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>68900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>106100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>67700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-502900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>64700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>98900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1604900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>90900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>40100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>76600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>136600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>168400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>143500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>189600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-333500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-61500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>130500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>199600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-110600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>186000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>219600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>223700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>115500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>234900</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>94400</v>
+      </c>
+      <c r="E27" s="3">
         <v>134200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>112800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>52600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>87100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>51600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-520500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>46200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>80500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1623600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>72700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>22500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>58100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>117800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>149800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>27000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>69700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-268700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-65800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>74500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>56300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-40800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>82800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>101100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>82700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>33300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>66600</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2529,17 +2590,17 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>3</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>3</v>
+      <c r="T29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>3</v>
@@ -2547,12 +2608,12 @@
       <c r="W29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,186 +2816,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>49900</v>
+      </c>
+      <c r="E32" s="3">
         <v>39800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>35500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>60200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>112900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>112400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>98600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>90900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>81200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-31100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-16800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-9100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-42300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-84300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-70800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-59700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-52500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-46200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-39100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-34500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>18900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>19400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>8000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2300</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>94400</v>
+      </c>
+      <c r="E33" s="3">
         <v>134200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>112800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>52600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>87100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>51600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-520500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>46200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>80500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1623600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>72700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>22500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>58100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>117800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>149800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>27000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>69700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-268700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-65800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>74500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>56300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-48200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>82800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>101100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>82700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>33300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>66600</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>94400</v>
+      </c>
+      <c r="E35" s="3">
         <v>134200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>112800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>52600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>87100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>51600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-520500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>46200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>80500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1623600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>72700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>22500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>58100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>117800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>149800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>27000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>69700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-268700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-65800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>74500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>56300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-48200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>82800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>101100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>82700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>33300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>66600</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,83 +3351,84 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>51300</v>
+      </c>
+      <c r="E41" s="3">
         <v>258900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>180600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>107100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>52500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>67900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>48100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>114500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>41600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>134700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>194200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>242600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>231900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>208000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>182500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>202300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>76000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>88300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>153800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>25500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>29000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>294200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>184100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1847400</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3354,8 +3441,11 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,83 +3533,86 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>242000</v>
+      </c>
+      <c r="E43" s="3">
         <v>258300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>240000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>237600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>225700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>246900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>230900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>227600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>232000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>252300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>238500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>254900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>288700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>290400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>263700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>238500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>253200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>255300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>243500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>282800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>265100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>255500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>225800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>233900</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,8 +3625,11 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3621,83 +3717,86 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>68700</v>
+      </c>
+      <c r="E45" s="3">
         <v>78400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>67200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>71000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>43000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>74900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>53100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>49600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>52300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>59900</v>
-      </c>
-      <c r="M45" s="3">
-        <v>53000</v>
       </c>
       <c r="N45" s="3">
         <v>53000</v>
       </c>
       <c r="O45" s="3">
+        <v>53000</v>
+      </c>
+      <c r="P45" s="3">
         <v>51600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>63300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>86900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>62400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>39300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>31500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>24900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>25000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>16800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>19200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>10300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>14600</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3710,83 +3809,86 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>362000</v>
+      </c>
+      <c r="E46" s="3">
         <v>595500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>487800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>415700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>321200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>389700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>332100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>391700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>325900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>446800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>485800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>550600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>572200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>561700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>533000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>503200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>368400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>375200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>422200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>333300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>311000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>568800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>420300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2095900</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3799,83 +3901,86 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2194100</v>
+      </c>
+      <c r="E47" s="3">
         <v>1832300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1291000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1090200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>852000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>819700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>784400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1325700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1279000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1239000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3089100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2971700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2870200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2796300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2722100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2592400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2465800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2324100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2227300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2066300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1673300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1510300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1300400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1003300</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3888,83 +3993,86 @@
       <c r="AE47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8008100</v>
+      </c>
+      <c r="E48" s="3">
         <v>7992400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7949500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7910900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7900700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7884300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7858700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7822400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7783600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7787500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7773200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7762100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7816000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7881100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7838700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7806900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7750800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7787600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7679800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7446700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6055300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5867600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5620200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5401800</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3977,83 +4085,86 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>992600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1008800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1025000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1041200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1057400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1073700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1089900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1106100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1122300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1138500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1154700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1170900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1187100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1203300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1219500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1235700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1251900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1284100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1882400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2216100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1805000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1815400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1971400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1981800</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,83 +4361,86 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>292000</v>
+      </c>
+      <c r="E52" s="3">
         <v>280400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>279300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>269000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>267700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>278200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>321400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>316100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>308000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>270700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>365600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>351000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>343300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>283400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>317300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>307000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>352800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>270700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>364300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>374100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>430700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>761700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>630500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>580100</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,83 +4545,86 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11848800</v>
+      </c>
+      <c r="E54" s="3">
         <v>11709400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11032700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10727000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10399100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10445600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10386500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10961900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10818700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10882500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12868400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12806300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12788800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>12725900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>12630700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>12445300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12189700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>12041700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>12576000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>12436500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10275400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>10523800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9942800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>11062900</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4511,8 +4637,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,83 +4707,84 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>51900</v>
+      </c>
+      <c r="E57" s="3">
         <v>60900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>54000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>49500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>43900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>60500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>51200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>61300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>47600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>59600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>64200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>61800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>67700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>72100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>101100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>111700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>109200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>128100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>173000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>181100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>142500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>210000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>133600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>115500</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4666,37 +4797,40 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>299800</v>
+      </c>
+      <c r="E58" s="3">
         <v>299700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>299600</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>98900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>98800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>98900</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -4705,22 +4839,22 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>310000</v>
-      </c>
-      <c r="P58" s="3">
-        <v>302500</v>
       </c>
       <c r="Q58" s="3">
         <v>302500</v>
       </c>
       <c r="R58" s="3">
-        <v>0</v>
+        <v>302500</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
       <c r="T58" s="3">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="U58" s="3">
         <v>6000</v>
@@ -4734,8 +4868,8 @@
       <c r="X58" s="3">
         <v>6000</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
+      <c r="Y58" s="3">
+        <v>6000</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
@@ -4755,83 +4889,86 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>224500</v>
+      </c>
+      <c r="E59" s="3">
         <v>422300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>297300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>412400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>170000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>254000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>391100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>239100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>160100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>307900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>254000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>310700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>197200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>220300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>268700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>290900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>184000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>201800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>379400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>506800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>244800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>333400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>824700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>793000</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4844,83 +4981,86 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>576200</v>
+      </c>
+      <c r="E60" s="3">
         <v>782900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>650900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>461900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>312900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>413300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>541200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>300400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>207700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>367600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>318200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>372500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>574800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>594900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>672300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>402600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>293100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>336000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>558300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>693900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>393300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>549500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>958300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>908500</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4933,83 +5073,86 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7490200</v>
+      </c>
+      <c r="E61" s="3">
         <v>7276700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6884000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6910900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6830600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6870300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6727400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6848900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6885700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6939900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7077200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7079400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6911700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6928300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6925600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7225500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6582600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6324500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5978100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5394100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5115200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4660200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3477300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3714000</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5022,82 +5165,85 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1566300</v>
+      </c>
+      <c r="E62" s="3">
         <v>1461700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1343300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1254500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1153800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1081500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>994400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1093700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1005200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>920700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1132000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1027700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>940100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>839500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>711200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>600000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>269600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>99200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>98300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>103300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>89800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>54500</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>31800</v>
       </c>
       <c r="Z62" s="3">
         <v>31800</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
+      <c r="AA62" s="3">
+        <v>31800</v>
       </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,83 +5533,86 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10090200</v>
+      </c>
+      <c r="E66" s="3">
         <v>9983900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9343600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9092700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8773100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8844500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8740900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8734000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8585500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8711400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9006600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8955200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8899100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8833900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8776200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8691200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11752800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11369000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11430900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11110200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8912200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10066000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9684600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9677600</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5467,8 +5625,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5726,11 +5894,11 @@
         <v>681800</v>
       </c>
       <c r="R70" s="3">
+        <v>681800</v>
+      </c>
+      <c r="S70" s="3">
         <v>669500</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,83 +6027,86 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2904500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2932200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3000900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3047300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3031700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3053600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3003800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2417000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2407300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2464600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-770800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-778200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-735900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-729000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-781400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-866100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-858400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-618100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-234300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-53800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-13700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>33900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>258200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1385300</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5945,8 +6119,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,83 +6395,86 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1076800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1043700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1007200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>952500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>944200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>919200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>963800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1546100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1551300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1489300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3180000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3169300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3207900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3210100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3172600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3084600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>436900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>672700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1145100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1326200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1363200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>457800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>258200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1385300</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6301,8 +6487,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>94400</v>
+      </c>
+      <c r="E81" s="3">
         <v>134200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>112800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>52600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>87100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>51600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-520500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>46200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>80500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1623600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>72700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>22500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>58100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>117800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>149800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>27000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>69700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-268700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-65800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>74500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>56300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-48200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>82800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>101100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>82700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>33300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>66600</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,97 +6804,101 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>87900</v>
+      </c>
+      <c r="E83" s="3">
         <v>86800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>85600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>86200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>85600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>85100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>84800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>83900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>83200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>82700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>82200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>85500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>84800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>84500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>83000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>79400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>75900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>75200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>74000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>70500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>60900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>59000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>54100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>52600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>51700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>22200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>41900</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>177500</v>
+      </c>
+      <c r="E89" s="3">
         <v>291200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>201600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>298600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>224700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>99200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>209600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>351000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>185900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>346700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>209900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>382600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>229600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>316700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>231200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>343700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>249300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>286000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>267900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>300300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>122200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>20300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>251800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>154900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>294700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>160000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>320500</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,97 +7482,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-84900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-107100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-107500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-96300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-75600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-99800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-113700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-91900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-71300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-79400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-80700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-69100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-61300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-84400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-108500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-116700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-152400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-197400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-287400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-273600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-209000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-241500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-241400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-212400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-170600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-75200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-149400</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,97 +7756,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-506400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-514500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-316000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-130900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-108700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-139900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-155000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-129700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-142500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-186800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-173700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-141700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-70700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-211700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-172900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-148900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-196300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-458000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-486500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1277500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-352600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-718800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-503500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-277100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-286500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-117600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-207300</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,13 +7884,14 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-65000</v>
+        <v>-65100</v>
       </c>
       <c r="E96" s="3">
         <v>-65000</v>
@@ -7669,7 +7903,7 @@
         <v>-65000</v>
       </c>
       <c r="H96" s="3">
-        <v>-64900</v>
+        <v>-65000</v>
       </c>
       <c r="I96" s="3">
         <v>-64900</v>
@@ -7693,20 +7927,20 @@
         <v>-64900</v>
       </c>
       <c r="P96" s="3">
+        <v>-64900</v>
+      </c>
+      <c r="Q96" s="3">
         <v>213500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-64900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-34400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-114300</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -7717,11 +7951,11 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>20800</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,97 +8250,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>121300</v>
+      </c>
+      <c r="E100" s="3">
         <v>301500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>187900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-113100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-131400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>60500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-121000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-148400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-136500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-219500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-84600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-230200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-135000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-79500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-78100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-68400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-65300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>106500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>346800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>923600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>15300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>808600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1411500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1803200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>37100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-197500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-718900</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,93 +8434,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-207600</v>
+      </c>
+      <c r="E102" s="3">
         <v>78300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>73500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>54600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-15400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>19800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-66500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>72900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-93100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-59600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-48400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>10700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>23900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>25500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-19800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>126400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-12400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-65400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>128300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-53500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-215100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>110100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1663300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1681100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>45300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-155100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-605700</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
